--- a/output/2026-09-20_02_Croazia_Sibensko-kninska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_02_Croazia_Sibensko-kninska_ATEX_Equipment-Services.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,6 @@
           <t>Belcom Šibenik d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Šibenik</t>
@@ -596,7 +595,6 @@
           <t>UNIELEKTRO d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Vodice</t>
